--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/57.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/57.xlsx
@@ -426,13 +426,13 @@
         <v>-10.02969451320102</v>
       </c>
       <c r="E2">
-        <v>-14.9120414919559</v>
+        <v>-14.61647405481316</v>
       </c>
       <c r="F2">
-        <v>-1.648430569633454</v>
+        <v>-1.770540208480129</v>
       </c>
       <c r="G2">
-        <v>-3.874820889930912</v>
+        <v>-4.048344029179257</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-8.566504697412292</v>
       </c>
       <c r="E3">
-        <v>-15.13602002549258</v>
+        <v>-16.1329361058478</v>
       </c>
       <c r="F3">
-        <v>-1.761445562764793</v>
+        <v>-1.808928410660664</v>
       </c>
       <c r="G3">
-        <v>-3.413922650560363</v>
+        <v>-3.226460745940065</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-7.165433829980818</v>
       </c>
       <c r="E4">
-        <v>-16.17365003646509</v>
+        <v>-15.11433195595433</v>
       </c>
       <c r="F4">
-        <v>-1.895002410750755</v>
+        <v>-2.075134215959118</v>
       </c>
       <c r="G4">
-        <v>-2.070224624406177</v>
+        <v>-2.3507491307213</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-6.017447574780241</v>
       </c>
       <c r="E5">
-        <v>-15.24606766596656</v>
+        <v>-15.78407881419618</v>
       </c>
       <c r="F5">
-        <v>-2.035995512911648</v>
+        <v>-1.900232722532031</v>
       </c>
       <c r="G5">
-        <v>-0.7718230169078071</v>
+        <v>-2.097726207928965</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-5.096596315061735</v>
       </c>
       <c r="E6">
-        <v>-16.17399059979373</v>
+        <v>-15.64409067328151</v>
       </c>
       <c r="F6">
-        <v>-2.177413567550176</v>
+        <v>-2.187808750087907</v>
       </c>
       <c r="G6">
-        <v>-0.4798973889632928</v>
+        <v>-0.4538317149656177</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-4.432600450222494</v>
       </c>
       <c r="E7">
-        <v>-17.4610874022034</v>
+        <v>-16.84361286169583</v>
       </c>
       <c r="F7">
-        <v>-2.787066296621126</v>
+        <v>-2.498918695557318</v>
       </c>
       <c r="G7">
-        <v>0.1650009076997377</v>
+        <v>-0.021247000685693</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-3.991319211458306</v>
       </c>
       <c r="E8">
-        <v>-17.13979497411466</v>
+        <v>-16.81618505410667</v>
       </c>
       <c r="F8">
-        <v>-2.396558992328188</v>
+        <v>-2.320990347640401</v>
       </c>
       <c r="G8">
-        <v>0.9407784414598683</v>
+        <v>0.8367559339715506</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-3.76536530152883</v>
       </c>
       <c r="E9">
-        <v>-16.54883868791613</v>
+        <v>-16.59233527012106</v>
       </c>
       <c r="F9">
-        <v>-2.163191327611512</v>
+        <v>-2.48615438224758</v>
       </c>
       <c r="G9">
-        <v>0.8881066693341578</v>
+        <v>1.195994389708739</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-3.704739554617859</v>
       </c>
       <c r="E10">
-        <v>-19.11243745064582</v>
+        <v>-16.9049142608503</v>
       </c>
       <c r="F10">
-        <v>-2.698074786538375</v>
+        <v>-2.23039511826583</v>
       </c>
       <c r="G10">
-        <v>1.568628575942929</v>
+        <v>1.542748264811223</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-3.776667850517424</v>
       </c>
       <c r="E11">
-        <v>-17.00688805850882</v>
+        <v>-17.1739592904727</v>
       </c>
       <c r="F11">
-        <v>-2.368305865320905</v>
+        <v>-2.035171287345862</v>
       </c>
       <c r="G11">
-        <v>2.208067805665942</v>
+        <v>1.806255937881469</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-3.935229669020453</v>
       </c>
       <c r="E12">
-        <v>-18.8894889135177</v>
+        <v>-17.58262282520185</v>
       </c>
       <c r="F12">
-        <v>-1.771748796520814</v>
+        <v>-1.618377400259888</v>
       </c>
       <c r="G12">
-        <v>1.491342703812202</v>
+        <v>1.918883459542096</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-4.136376403741585</v>
       </c>
       <c r="E13">
-        <v>-19.51836817232324</v>
+        <v>-18.03785216530498</v>
       </c>
       <c r="F13">
-        <v>-2.542362423997138</v>
+        <v>-1.510900043216263</v>
       </c>
       <c r="G13">
-        <v>1.190611034361863</v>
+        <v>2.21580344188941</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-4.356877613586798</v>
       </c>
       <c r="E14">
-        <v>-19.54168845391215</v>
+        <v>-18.41027893122501</v>
       </c>
       <c r="F14">
-        <v>-1.352862453375368</v>
+        <v>-1.060500947333519</v>
       </c>
       <c r="G14">
-        <v>0.7211834924121476</v>
+        <v>2.141206636687531</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-4.567525073589786</v>
       </c>
       <c r="E15">
-        <v>-20.7014353374686</v>
+        <v>-18.9275614017324</v>
       </c>
       <c r="F15">
-        <v>-0.7517833269233934</v>
+        <v>-1.176396173924392</v>
       </c>
       <c r="G15">
-        <v>1.930885052427444</v>
+        <v>1.926718304060027</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-4.766732523629821</v>
       </c>
       <c r="E16">
-        <v>-20.91586148495817</v>
+        <v>-18.97896569829981</v>
       </c>
       <c r="F16">
-        <v>-0.7912682875452347</v>
+        <v>-0.4122214462700285</v>
       </c>
       <c r="G16">
-        <v>2.416768117534946</v>
+        <v>1.893251169146546</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-4.949702306017013</v>
       </c>
       <c r="E17">
-        <v>-21.91301429835891</v>
+        <v>-20.18681092220909</v>
       </c>
       <c r="F17">
-        <v>-0.02638033555706081</v>
+        <v>-0.2126669105682248</v>
       </c>
       <c r="G17">
-        <v>1.33095683134634</v>
+        <v>1.854622592176434</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-5.125894984969201</v>
       </c>
       <c r="E18">
-        <v>-21.79338935256987</v>
+        <v>-19.76173389632422</v>
       </c>
       <c r="F18">
-        <v>-0.2802757728825121</v>
+        <v>0.2426203813584394</v>
       </c>
       <c r="G18">
-        <v>1.899373365212707</v>
+        <v>1.073613126255712</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-5.30455728315097</v>
       </c>
       <c r="E19">
-        <v>-22.1280135890113</v>
+        <v>-21.26372615910316</v>
       </c>
       <c r="F19">
-        <v>-0.05508409443146647</v>
+        <v>0.75920768945967</v>
       </c>
       <c r="G19">
-        <v>1.916058633894512</v>
+        <v>0.7187320032410922</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-5.48787557962391</v>
       </c>
       <c r="E20">
-        <v>-21.87256202005507</v>
+        <v>-21.9265952993911</v>
       </c>
       <c r="F20">
-        <v>0.3979897997949175</v>
+        <v>1.306395717787717</v>
       </c>
       <c r="G20">
-        <v>2.425002405975318</v>
+        <v>1.015085454012135</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-5.684276851974355</v>
       </c>
       <c r="E21">
-        <v>-24.25039179343651</v>
+        <v>-22.97806796370926</v>
       </c>
       <c r="F21">
-        <v>0.6690697188914445</v>
+        <v>1.78209066904975</v>
       </c>
       <c r="G21">
-        <v>2.614469362441591</v>
+        <v>0.6325748209897627</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-5.885293388497307</v>
       </c>
       <c r="E22">
-        <v>-24.24247577265139</v>
+        <v>-22.48251924806469</v>
       </c>
       <c r="F22">
-        <v>1.379706232935473</v>
+        <v>2.074305554061303</v>
       </c>
       <c r="G22">
-        <v>1.051912617214379</v>
+        <v>-0.1391691123770979</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-6.08974296587385</v>
       </c>
       <c r="E23">
-        <v>-24.51971508821767</v>
+        <v>-23.25003270089301</v>
       </c>
       <c r="F23">
-        <v>1.193789109785958</v>
+        <v>2.253330660419527</v>
       </c>
       <c r="G23">
-        <v>0.6162550565507136</v>
+        <v>-0.5095423937953841</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-6.28626283243561</v>
       </c>
       <c r="E24">
-        <v>-25.06525185536787</v>
+        <v>-24.21251035294275</v>
       </c>
       <c r="F24">
-        <v>1.442865933929324</v>
+        <v>2.274611418997446</v>
       </c>
       <c r="G24">
-        <v>0.2952875057746551</v>
+        <v>-0.5540999717319146</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-6.461409677887116</v>
       </c>
       <c r="E25">
-        <v>-23.75013748936091</v>
+        <v>-24.19915777853343</v>
       </c>
       <c r="F25">
-        <v>2.484897454402518</v>
+        <v>2.778797238711365</v>
       </c>
       <c r="G25">
-        <v>-0.3552839388848646</v>
+        <v>-0.9125552040917687</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-6.608555869620658</v>
       </c>
       <c r="E26">
-        <v>-24.93736201904242</v>
+        <v>-24.01030710638215</v>
       </c>
       <c r="F26">
-        <v>1.996054655723251</v>
+        <v>3.212058241397591</v>
       </c>
       <c r="G26">
-        <v>-0.05763294805203886</v>
+        <v>-1.064698955883487</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-6.711934168049632</v>
       </c>
       <c r="E27">
-        <v>-25.64914352910287</v>
+        <v>-25.21259948675014</v>
       </c>
       <c r="F27">
-        <v>1.43916313163881</v>
+        <v>3.154549662825638</v>
       </c>
       <c r="G27">
-        <v>0.00127589290184132</v>
+        <v>-1.008573168663733</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-6.770556238395332</v>
       </c>
       <c r="E28">
-        <v>-24.40624935482335</v>
+        <v>-24.43498542397984</v>
       </c>
       <c r="F28">
-        <v>2.452634200798283</v>
+        <v>3.200696354100793</v>
       </c>
       <c r="G28">
-        <v>-0.0972170575424985</v>
+        <v>-1.252367109326483</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-6.777246979238276</v>
       </c>
       <c r="E29">
-        <v>-25.1439925888753</v>
+        <v>-24.20559525608691</v>
       </c>
       <c r="F29">
-        <v>2.113149358313378</v>
+        <v>3.12270887659683</v>
       </c>
       <c r="G29">
-        <v>0.8644167729143958</v>
+        <v>-1.091372933370891</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-6.734012458075922</v>
       </c>
       <c r="E30">
-        <v>-25.49689095514598</v>
+        <v>-24.46876349168467</v>
       </c>
       <c r="F30">
-        <v>2.265759484931131</v>
+        <v>3.122201915746317</v>
       </c>
       <c r="G30">
-        <v>-0.03756937586933326</v>
+        <v>-0.6697376819060954</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-6.647144697092958</v>
       </c>
       <c r="E31">
-        <v>-24.56491448706577</v>
+        <v>-24.33442787138309</v>
       </c>
       <c r="F31">
-        <v>1.638233072409977</v>
+        <v>2.914902973195741</v>
       </c>
       <c r="G31">
-        <v>1.500743995084801</v>
+        <v>-0.350777793720603</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-6.516592767879852</v>
       </c>
       <c r="E32">
-        <v>-24.02540818275922</v>
+        <v>-24.27816016435431</v>
       </c>
       <c r="F32">
-        <v>1.396020100566207</v>
+        <v>2.684984630344321</v>
       </c>
       <c r="G32">
-        <v>0.131591209167261</v>
+        <v>0.04862696755086298</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-6.353956041572204</v>
       </c>
       <c r="E33">
-        <v>-23.7037834977645</v>
+        <v>-22.70595786412914</v>
       </c>
       <c r="F33">
-        <v>1.926143760396584</v>
+        <v>2.487978981140932</v>
       </c>
       <c r="G33">
-        <v>0.8596208351005207</v>
+        <v>-0.2395339666932659</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-6.159765414996999</v>
       </c>
       <c r="E34">
-        <v>-23.56553555239493</v>
+        <v>-22.92275549528519</v>
       </c>
       <c r="F34">
-        <v>0.9986158092775607</v>
+        <v>2.338437127383148</v>
       </c>
       <c r="G34">
-        <v>1.159381307562966</v>
+        <v>0.3383595700388421</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-5.941765599781717</v>
       </c>
       <c r="E35">
-        <v>-23.39219712454189</v>
+        <v>-23.09072382089524</v>
       </c>
       <c r="F35">
-        <v>1.481835650026624</v>
+        <v>2.014066676529723</v>
       </c>
       <c r="G35">
-        <v>0.9401570842471834</v>
+        <v>0.4816737836234148</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-5.704902818475851</v>
       </c>
       <c r="E36">
-        <v>-22.33763447099805</v>
+        <v>-22.56913447024399</v>
       </c>
       <c r="F36">
-        <v>1.405171903632336</v>
+        <v>2.098747362648306</v>
       </c>
       <c r="G36">
-        <v>0.7722627103372791</v>
+        <v>0.7030179315471814</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-5.447748368846252</v>
       </c>
       <c r="E37">
-        <v>-22.80305579169231</v>
+        <v>-21.90189199843102</v>
       </c>
       <c r="F37">
-        <v>0.6351571857882355</v>
+        <v>1.616647474627827</v>
       </c>
       <c r="G37">
-        <v>2.291063376217433</v>
+        <v>1.257715002587248</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-5.179299326600765</v>
       </c>
       <c r="E38">
-        <v>-23.77081217533591</v>
+        <v>-21.25614239522402</v>
       </c>
       <c r="F38">
-        <v>0.8104422133228194</v>
+        <v>1.589520098920949</v>
       </c>
       <c r="G38">
-        <v>2.728091577791433</v>
+        <v>1.49574441919282</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-4.896828615420983</v>
       </c>
       <c r="E39">
-        <v>-22.62616221494521</v>
+        <v>-20.93672721865411</v>
       </c>
       <c r="F39">
-        <v>1.591577763549503</v>
+        <v>1.100624284727903</v>
       </c>
       <c r="G39">
-        <v>2.882000192926743</v>
+        <v>2.267052358212964</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-4.607384822895004</v>
       </c>
       <c r="E40">
-        <v>-20.51354405713336</v>
+        <v>-20.20079478473979</v>
       </c>
       <c r="F40">
-        <v>0.3716328057726428</v>
+        <v>0.9695467403785204</v>
       </c>
       <c r="G40">
-        <v>2.315815845685778</v>
+        <v>2.452167203445851</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-4.312437585064064</v>
       </c>
       <c r="E41">
-        <v>-21.13572003286062</v>
+        <v>-19.87421947184587</v>
       </c>
       <c r="F41">
-        <v>0.6738634810514452</v>
+        <v>1.173694573328847</v>
       </c>
       <c r="G41">
-        <v>3.336415953477557</v>
+        <v>2.432693659540738</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-4.01405073040447</v>
       </c>
       <c r="E42">
-        <v>-19.10008580016578</v>
+        <v>-20.07633550096865</v>
       </c>
       <c r="F42">
-        <v>0.3034971017901751</v>
+        <v>0.7769861106585529</v>
       </c>
       <c r="G42">
-        <v>3.010508873935112</v>
+        <v>2.842423915670057</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-3.721328041658173</v>
       </c>
       <c r="E43">
-        <v>-19.59752007375182</v>
+        <v>-18.87599512992333</v>
       </c>
       <c r="F43">
-        <v>-0.5488904705883078</v>
+        <v>0.1249259407686857</v>
       </c>
       <c r="G43">
-        <v>2.498771605141815</v>
+        <v>3.408415067811279</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-3.435463756441616</v>
       </c>
       <c r="E44">
-        <v>-21.18038782065915</v>
+        <v>-18.43633617907699</v>
       </c>
       <c r="F44">
-        <v>0.715787983674531</v>
+        <v>0.4496418208290779</v>
       </c>
       <c r="G44">
-        <v>3.355325576550991</v>
+        <v>3.104135396461617</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-3.16868177142952</v>
       </c>
       <c r="E45">
-        <v>-19.08429529070878</v>
+        <v>-18.83387741387825</v>
       </c>
       <c r="F45">
-        <v>-0.1672864591406595</v>
+        <v>-0.01749112495761931</v>
       </c>
       <c r="G45">
-        <v>3.69608779281687</v>
+        <v>3.519541411332016</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-2.923925382378063</v>
       </c>
       <c r="E46">
-        <v>-18.62401564563466</v>
+        <v>-18.26857136082186</v>
       </c>
       <c r="F46">
-        <v>0.3755219907287865</v>
+        <v>0.3368040983219376</v>
       </c>
       <c r="G46">
-        <v>2.759835621274779</v>
+        <v>2.974702511867994</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-2.708556959265846</v>
       </c>
       <c r="E47">
-        <v>-17.83628851328841</v>
+        <v>-18.12948446676468</v>
       </c>
       <c r="F47">
-        <v>-0.0793411770876444</v>
+        <v>-0.04994324632969274</v>
       </c>
       <c r="G47">
-        <v>3.853682779314832</v>
+        <v>2.553085535615336</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-2.52842572023454</v>
       </c>
       <c r="E48">
-        <v>-18.20787633052081</v>
+        <v>-17.31390589927412</v>
       </c>
       <c r="F48">
-        <v>0.06894072985048111</v>
+        <v>-0.2538442257939855</v>
       </c>
       <c r="G48">
-        <v>3.336460336135606</v>
+        <v>2.284505185804556</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-2.383815674275192</v>
       </c>
       <c r="E49">
-        <v>-18.01447789196885</v>
+        <v>-16.83494095644959</v>
       </c>
       <c r="F49">
-        <v>0.4169486445427898</v>
+        <v>-0.2562348941184648</v>
       </c>
       <c r="G49">
-        <v>2.646730333353978</v>
+        <v>2.493610163085184</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-2.282957986401008</v>
       </c>
       <c r="E50">
-        <v>-18.37028765937823</v>
+        <v>-16.61654849214481</v>
       </c>
       <c r="F50">
-        <v>-0.0238745241635923</v>
+        <v>-0.1762286852538802</v>
       </c>
       <c r="G50">
-        <v>2.062014921005291</v>
+        <v>2.847358222947261</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-2.222763960226602</v>
       </c>
       <c r="E51">
-        <v>-16.56217464948016</v>
+        <v>-16.45839005168401</v>
       </c>
       <c r="F51">
-        <v>0.2848629770642002</v>
+        <v>-0.2260972312698132</v>
       </c>
       <c r="G51">
-        <v>2.926612596499687</v>
+        <v>2.998551663707814</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-2.206632150778619</v>
       </c>
       <c r="E52">
-        <v>-17.07204779098405</v>
+        <v>-14.9453793192603</v>
       </c>
       <c r="F52">
-        <v>0.06186564386317053</v>
+        <v>-0.472400681348607</v>
       </c>
       <c r="G52">
-        <v>2.748055941679676</v>
+        <v>2.711878853880619</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-2.230499979060048</v>
       </c>
       <c r="E53">
-        <v>-17.43697385725144</v>
+        <v>-16.31082230010153</v>
       </c>
       <c r="F53">
-        <v>0.09383068520239785</v>
+        <v>-0.7664677958728203</v>
       </c>
       <c r="G53">
-        <v>1.906263120188655</v>
+        <v>2.171183206082693</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-2.290957394410651</v>
       </c>
       <c r="E54">
-        <v>-16.358289352333</v>
+        <v>-14.98859348309514</v>
       </c>
       <c r="F54">
-        <v>0.03951297786602866</v>
+        <v>-0.4898494123211758</v>
       </c>
       <c r="G54">
-        <v>1.506208283514002</v>
+        <v>2.506063414784794</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-2.385999575897783</v>
       </c>
       <c r="E55">
-        <v>-15.44913893369405</v>
+        <v>-16.16333761274555</v>
       </c>
       <c r="F55">
-        <v>-0.3681986890156516</v>
+        <v>-0.6754716366752946</v>
       </c>
       <c r="G55">
-        <v>1.467313410595596</v>
+        <v>2.156476881800952</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-2.506798428403745</v>
       </c>
       <c r="E56">
-        <v>-15.15242105701433</v>
+        <v>-14.51592896185038</v>
       </c>
       <c r="F56">
-        <v>-0.3712984398369273</v>
+        <v>-0.9014171294628878</v>
       </c>
       <c r="G56">
-        <v>1.455079461441639</v>
+        <v>2.049402413885623</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-2.652310760717147</v>
       </c>
       <c r="E57">
-        <v>-15.01583024296337</v>
+        <v>-15.1369088127161</v>
       </c>
       <c r="F57">
-        <v>-0.5380802759817742</v>
+        <v>-0.9748485862514528</v>
       </c>
       <c r="G57">
-        <v>1.489752760356214</v>
+        <v>1.653216700695</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-2.813096301899363</v>
       </c>
       <c r="E58">
-        <v>-14.7230537638309</v>
+        <v>-14.90489381526587</v>
       </c>
       <c r="F58">
-        <v>-0.2670492305620124</v>
+        <v>-0.8406688059785861</v>
       </c>
       <c r="G58">
-        <v>1.983353186475048</v>
+        <v>1.454745286133976</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-2.98783795483678</v>
       </c>
       <c r="E59">
-        <v>-13.1087752796739</v>
+        <v>-15.28197217786971</v>
       </c>
       <c r="F59">
-        <v>-1.149349149855585</v>
+        <v>-1.2393951716421</v>
       </c>
       <c r="G59">
-        <v>1.061984869846894</v>
+        <v>1.840130348951164</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-3.171544427946527</v>
       </c>
       <c r="E60">
-        <v>-15.01404851530502</v>
+        <v>-14.5203812043906</v>
       </c>
       <c r="F60">
-        <v>-1.850993735742225</v>
+        <v>-1.210825608286948</v>
       </c>
       <c r="G60">
-        <v>0.439390164225744</v>
+        <v>1.564694183844121</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-3.359237470211926</v>
       </c>
       <c r="E61">
-        <v>-13.26013906640727</v>
+        <v>-15.20672429508646</v>
       </c>
       <c r="F61">
-        <v>-1.189228413361159</v>
+        <v>-1.191300988602964</v>
       </c>
       <c r="G61">
-        <v>-0.2339835236925591</v>
+        <v>0.795767243891072</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-3.552001265444307</v>
       </c>
       <c r="E62">
-        <v>-16.27927450687814</v>
+        <v>-14.72083179577212</v>
       </c>
       <c r="F62">
-        <v>-0.6054414564426244</v>
+        <v>-1.422907544221289</v>
       </c>
       <c r="G62">
-        <v>0.7607179977553761</v>
+        <v>1.206121467977667</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-3.743941909281808</v>
       </c>
       <c r="E63">
-        <v>-14.21299788102871</v>
+        <v>-14.70214234481039</v>
       </c>
       <c r="F63">
-        <v>-0.7297818887050386</v>
+        <v>-1.681729282491188</v>
       </c>
       <c r="G63">
-        <v>0.479258844876635</v>
+        <v>1.490601252348326</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-3.938333001895449</v>
       </c>
       <c r="E64">
-        <v>-13.75324154058152</v>
+        <v>-14.23309942384088</v>
       </c>
       <c r="F64">
-        <v>-1.156187322765695</v>
+        <v>-1.743532117679254</v>
       </c>
       <c r="G64">
-        <v>0.07404517688994193</v>
+        <v>1.457264654664401</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-4.130460097341619</v>
       </c>
       <c r="E65">
-        <v>-13.25981511592394</v>
+        <v>-13.65058661626573</v>
       </c>
       <c r="F65">
-        <v>-1.590534315116991</v>
+        <v>-1.712602535593526</v>
       </c>
       <c r="G65">
-        <v>-0.1751347298642745</v>
+        <v>0.916874463983635</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-4.319241374053344</v>
       </c>
       <c r="E66">
-        <v>-13.03314945466009</v>
+        <v>-15.09864112356913</v>
       </c>
       <c r="F66">
-        <v>-1.87257187821775</v>
+        <v>-1.773700430121809</v>
       </c>
       <c r="G66">
-        <v>0.3290339903593854</v>
+        <v>0.6471036146393081</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-4.503427005277262</v>
       </c>
       <c r="E67">
-        <v>-13.30211972647864</v>
+        <v>-14.72142155178025</v>
       </c>
       <c r="F67">
-        <v>-1.779629883991048</v>
+        <v>-1.936429064564758</v>
       </c>
       <c r="G67">
-        <v>0.6183071017993286</v>
+        <v>0.9780520419871928</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-4.67586190992731</v>
       </c>
       <c r="E68">
-        <v>-13.98221223413064</v>
+        <v>-14.42104054271202</v>
       </c>
       <c r="F68">
-        <v>-1.444297647296377</v>
+        <v>-2.139680603985256</v>
       </c>
       <c r="G68">
-        <v>-0.2499403946334435</v>
+        <v>0.8021191854812506</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-4.837501519283618</v>
       </c>
       <c r="E69">
-        <v>-14.20315477018887</v>
+        <v>-14.07533969166727</v>
       </c>
       <c r="F69">
-        <v>-1.448832958826705</v>
+        <v>-2.328761262246063</v>
       </c>
       <c r="G69">
-        <v>0.1830698710148327</v>
+        <v>0.9654160381662044</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-4.979266332547421</v>
       </c>
       <c r="E70">
-        <v>-15.19683134571072</v>
+        <v>-14.22204772850551</v>
       </c>
       <c r="F70">
-        <v>-1.762356766907873</v>
+        <v>-2.234305012407043</v>
       </c>
       <c r="G70">
-        <v>-1.007844770922813</v>
+        <v>0.2974726989974169</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-5.100795777477635</v>
       </c>
       <c r="E71">
-        <v>-14.29582537447977</v>
+        <v>-14.29936391052852</v>
       </c>
       <c r="F71">
-        <v>-2.33489449449639</v>
+        <v>-2.232716203728474</v>
       </c>
       <c r="G71">
-        <v>0.8041268480718167</v>
+        <v>0.5423631523884342</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-5.198803071106042</v>
       </c>
       <c r="E72">
-        <v>-13.83503488441269</v>
+        <v>-14.75510824883593</v>
       </c>
       <c r="F72">
-        <v>-1.961038203367126</v>
+        <v>-2.390984079707347</v>
       </c>
       <c r="G72">
-        <v>0.6460514845690895</v>
+        <v>0.7860761599688595</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-5.268543826012974</v>
       </c>
       <c r="E73">
-        <v>-15.0484204922293</v>
+        <v>-13.94525280655099</v>
       </c>
       <c r="F73">
-        <v>-2.262027984276535</v>
+        <v>-2.46136714445361</v>
       </c>
       <c r="G73">
-        <v>0.3863189481775932</v>
+        <v>0.6840952547507922</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-5.313779657970331</v>
       </c>
       <c r="E74">
-        <v>-14.42518960082553</v>
+        <v>-14.8243879669454</v>
       </c>
       <c r="F74">
-        <v>-2.135653081672845</v>
+        <v>-2.77226088603089</v>
       </c>
       <c r="G74">
-        <v>-0.7798484457808893</v>
+        <v>0.5694209093307323</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-5.329723478189194</v>
       </c>
       <c r="E75">
-        <v>-14.40740554993261</v>
+        <v>-14.80976035665935</v>
       </c>
       <c r="F75">
-        <v>-2.065068723647702</v>
+        <v>-2.624828884048037</v>
       </c>
       <c r="G75">
-        <v>0.3141475247008575</v>
+        <v>0.7265276865901565</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-5.32256105105705</v>
       </c>
       <c r="E76">
-        <v>-15.65069012607666</v>
+        <v>-15.1719868355656</v>
       </c>
       <c r="F76">
-        <v>-2.075352076586055</v>
+        <v>-2.393868455003895</v>
       </c>
       <c r="G76">
-        <v>0.7642242277412412</v>
+        <v>0.3988270255136169</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-5.292870406057276</v>
       </c>
       <c r="E77">
-        <v>-15.30251396108231</v>
+        <v>-16.11605330181237</v>
       </c>
       <c r="F77">
-        <v>-2.360376732541309</v>
+        <v>-2.468954161495851</v>
       </c>
       <c r="G77">
-        <v>-0.1156436928665761</v>
+        <v>1.350312891744854</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-5.24403671024429</v>
       </c>
       <c r="E78">
-        <v>-16.62615071672781</v>
+        <v>-16.77803365487679</v>
       </c>
       <c r="F78">
-        <v>-2.06972580518624</v>
+        <v>-2.352109625861369</v>
       </c>
       <c r="G78">
-        <v>0.7309555094166846</v>
+        <v>1.257547914933417</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-5.184609910823667</v>
       </c>
       <c r="E79">
-        <v>-15.93605727620563</v>
+        <v>-16.46223592537081</v>
       </c>
       <c r="F79">
-        <v>-2.692033503069758</v>
+        <v>-2.346876828977885</v>
       </c>
       <c r="G79">
-        <v>1.546580837870977</v>
+        <v>1.371347660915454</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-5.11504564516359</v>
       </c>
       <c r="E80">
-        <v>-15.99852572774237</v>
+        <v>-18.45022451774721</v>
       </c>
       <c r="F80">
-        <v>-2.146386238110918</v>
+        <v>-2.530561501976856</v>
       </c>
       <c r="G80">
-        <v>1.018424596344168</v>
+        <v>0.9384131068603196</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-5.047706123092055</v>
       </c>
       <c r="E81">
-        <v>-17.6674729325681</v>
+        <v>-18.63723531728159</v>
       </c>
       <c r="F81">
-        <v>-2.494820762015669</v>
+        <v>-2.643099355484183</v>
       </c>
       <c r="G81">
-        <v>1.416398669579704</v>
+        <v>1.985076277905183</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-4.983546049369369</v>
       </c>
       <c r="E82">
-        <v>-19.45006030566378</v>
+        <v>-20.00837650406049</v>
       </c>
       <c r="F82">
-        <v>-2.361094927079536</v>
+        <v>-2.290369746595917</v>
       </c>
       <c r="G82">
-        <v>1.514797633218764</v>
+        <v>1.252261157136412</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-4.932930859847801</v>
       </c>
       <c r="E83">
-        <v>-20.65498997522304</v>
+        <v>-21.12012472433589</v>
       </c>
       <c r="F83">
-        <v>-2.68099716416226</v>
+        <v>-2.181919057854003</v>
       </c>
       <c r="G83">
-        <v>2.163228267313571</v>
+        <v>1.645747360419825</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-4.903260290023544</v>
       </c>
       <c r="E84">
-        <v>-21.04153765964748</v>
+        <v>-21.77967129556396</v>
       </c>
       <c r="F84">
-        <v>-2.728171031016887</v>
+        <v>-2.369696694190206</v>
       </c>
       <c r="G84">
-        <v>1.320482524046793</v>
+        <v>2.068009190586487</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-4.89653936272362</v>
       </c>
       <c r="E85">
-        <v>-21.00548778534797</v>
+        <v>-22.61810083176372</v>
       </c>
       <c r="F85">
-        <v>-2.353847540672443</v>
+        <v>-2.464757652233269</v>
       </c>
       <c r="G85">
-        <v>1.978450208132937</v>
+        <v>2.21066810727869</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-4.925377640499256</v>
       </c>
       <c r="E86">
-        <v>-22.83111488740285</v>
+        <v>-23.98560380542207</v>
       </c>
       <c r="F86">
-        <v>-2.492989241688079</v>
+        <v>-2.051139725769628</v>
       </c>
       <c r="G86">
-        <v>2.399153423778705</v>
+        <v>2.570587967354159</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-4.987056969371646</v>
       </c>
       <c r="E87">
-        <v>-24.03390980634115</v>
+        <v>-25.38970903048612</v>
       </c>
       <c r="F87">
-        <v>-2.503118518289511</v>
+        <v>-2.05665002573305</v>
       </c>
       <c r="G87">
-        <v>2.340847664825372</v>
+        <v>2.353457561200449</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-5.093537067564056</v>
       </c>
       <c r="E88">
-        <v>-24.26808447368028</v>
+        <v>-26.63588008850093</v>
       </c>
       <c r="F88">
-        <v>-2.145321785998321</v>
+        <v>-2.153575638799815</v>
       </c>
       <c r="G88">
-        <v>1.128587575110785</v>
+        <v>2.145080981660743</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-5.245465200017912</v>
       </c>
       <c r="E89">
-        <v>-27.51854547852144</v>
+        <v>-29.09369655878724</v>
       </c>
       <c r="F89">
-        <v>-2.182359749312292</v>
+        <v>-1.938591103486065</v>
       </c>
       <c r="G89">
-        <v>1.993396720917061</v>
+        <v>2.667754659546214</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-5.447870055756516</v>
       </c>
       <c r="E90">
-        <v>-29.16848758832475</v>
+        <v>-29.77357725266167</v>
       </c>
       <c r="F90">
-        <v>-2.332677783326499</v>
+        <v>-1.875923452729477</v>
       </c>
       <c r="G90">
-        <v>2.898087601097183</v>
+        <v>2.22930882365924</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-5.711124412230507</v>
       </c>
       <c r="E91">
-        <v>-31.77422067994483</v>
+        <v>-32.00238357389127</v>
       </c>
       <c r="F91">
-        <v>-2.567051914437577</v>
+        <v>-2.149478533625568</v>
       </c>
       <c r="G91">
-        <v>2.991150202792007</v>
+        <v>2.8909733220864</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-6.031835081100341</v>
       </c>
       <c r="E92">
-        <v>-33.50800574336812</v>
+        <v>-33.1480095389433</v>
       </c>
       <c r="F92">
-        <v>-1.447264859333205</v>
+        <v>-1.359717193633534</v>
       </c>
       <c r="G92">
-        <v>2.321254026669067</v>
+        <v>2.289619634458548</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-6.424768306736672</v>
       </c>
       <c r="E93">
-        <v>-35.154247341881</v>
+        <v>-36.17829219861</v>
       </c>
       <c r="F93">
-        <v>-1.723826085534057</v>
+        <v>-1.508694929190011</v>
       </c>
       <c r="G93">
-        <v>2.466988400489602</v>
+        <v>2.267308211182893</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-6.8810435698952</v>
       </c>
       <c r="E94">
-        <v>-35.02536281144326</v>
+        <v>-37.80198808944606</v>
       </c>
       <c r="F94">
-        <v>-2.291161665832993</v>
+        <v>-1.491660381918842</v>
       </c>
       <c r="G94">
-        <v>2.384896147566636</v>
+        <v>1.487567567133453</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-7.40652187478028</v>
       </c>
       <c r="E95">
-        <v>-39.5260463319466</v>
+        <v>-40.46225284576113</v>
       </c>
       <c r="F95">
-        <v>-2.246773598553982</v>
+        <v>-1.558693528888184</v>
       </c>
       <c r="G95">
-        <v>2.177814497344121</v>
+        <v>1.494326784879845</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-8.001371119966397</v>
       </c>
       <c r="E96">
-        <v>-41.10033562086249</v>
+        <v>-41.96786878542099</v>
       </c>
       <c r="F96">
-        <v>-2.359448132682771</v>
+        <v>-1.743251301129705</v>
       </c>
       <c r="G96">
-        <v>0.8521410518469812</v>
+        <v>1.631544909844168</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-8.64556532409749</v>
       </c>
       <c r="E97">
-        <v>-43.0214055957676</v>
+        <v>-44.58569810502463</v>
       </c>
       <c r="F97">
-        <v>-1.966328985968806</v>
+        <v>-1.699926029228485</v>
       </c>
       <c r="G97">
-        <v>1.77122235621332</v>
+        <v>1.405733777925007</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-9.351810933730022</v>
       </c>
       <c r="E98">
-        <v>-44.21420373504703</v>
+        <v>-46.57837567298676</v>
       </c>
       <c r="F98">
-        <v>-2.357020187825165</v>
+        <v>-1.531062505800403</v>
       </c>
       <c r="G98">
-        <v>0.95473548204396</v>
+        <v>1.399966643123237</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-10.07232294344846</v>
       </c>
       <c r="E99">
-        <v>-48.04599699714426</v>
+        <v>-48.34661058604667</v>
       </c>
       <c r="F99">
-        <v>-2.131544379354959</v>
+        <v>-1.318046171435705</v>
       </c>
       <c r="G99">
-        <v>0.2326714075013941</v>
+        <v>1.259560799013165</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-10.83553700747129</v>
       </c>
       <c r="E100">
-        <v>-48.9438018807466</v>
+        <v>-50.32664058722187</v>
       </c>
       <c r="F100">
-        <v>-2.358628048953999</v>
+        <v>-1.624311824333543</v>
       </c>
       <c r="G100">
-        <v>1.022207565256692</v>
+        <v>1.041138074286854</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-11.55979006376657</v>
       </c>
       <c r="E101">
-        <v>-50.50343760180566</v>
+        <v>-52.56813912226015</v>
       </c>
       <c r="F101">
-        <v>-2.585033285650146</v>
+        <v>-1.656746549990158</v>
       </c>
       <c r="G101">
-        <v>-0.3082565965651409</v>
+        <v>0.633204010436221</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-12.32022000330166</v>
       </c>
       <c r="E102">
-        <v>-52.22299480153292</v>
+        <v>-54.23290819649309</v>
       </c>
       <c r="F102">
-        <v>-2.384639613769306</v>
+        <v>-2.017185774296279</v>
       </c>
       <c r="G102">
-        <v>0.02872265078821529</v>
+        <v>0.08394512037944352</v>
       </c>
     </row>
   </sheetData>
